--- a/artfynd/A 23809-2026 artfynd.xlsx
+++ b/artfynd/A 23809-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134413066</v>
       </c>
       <c r="B2" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134414533</v>
+        <v>134414404</v>
       </c>
       <c r="B3" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511451</v>
+        <v>511387</v>
       </c>
       <c r="R3" t="n">
-        <v>6976389</v>
+        <v>6976418</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134414404</v>
+        <v>134414533</v>
       </c>
       <c r="B4" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511387</v>
+        <v>511451</v>
       </c>
       <c r="R4" t="n">
-        <v>6976418</v>
+        <v>6976389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134414747</v>
+        <v>134413390</v>
       </c>
       <c r="B5" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511458</v>
+        <v>511381</v>
       </c>
       <c r="R5" t="n">
-        <v>6976416</v>
+        <v>6976427</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1066,7 @@
         <v>134413080</v>
       </c>
       <c r="B6" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134413390</v>
+        <v>134414747</v>
       </c>
       <c r="B7" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511381</v>
+        <v>511458</v>
       </c>
       <c r="R7" t="n">
-        <v>6976427</v>
+        <v>6976416</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1265,7 @@
         <v>134415071</v>
       </c>
       <c r="B8" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>134414632</v>
       </c>
       <c r="B9" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>134414325</v>
       </c>
       <c r="B10" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134413055</v>
+        <v>134413505</v>
       </c>
       <c r="B11" t="n">
-        <v>41675</v>
+        <v>58415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100453</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511428</v>
+        <v>511368</v>
       </c>
       <c r="R11" t="n">
-        <v>6976422</v>
+        <v>6976471</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134413505</v>
+        <v>134413055</v>
       </c>
       <c r="B12" t="n">
-        <v>58415</v>
+        <v>41675</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102999</v>
+        <v>100453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511368</v>
+        <v>511428</v>
       </c>
       <c r="R12" t="n">
-        <v>6976471</v>
+        <v>6976422</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134414651</v>
+        <v>134414708</v>
       </c>
       <c r="B13" t="n">
-        <v>92231</v>
+        <v>101298</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511450</v>
+        <v>511459</v>
       </c>
       <c r="R13" t="n">
-        <v>6976390</v>
+        <v>6976405</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1818,6 +1818,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1844,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134414708</v>
+        <v>134414148</v>
       </c>
       <c r="B14" t="n">
-        <v>101291</v>
+        <v>92399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,13 +1884,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511459</v>
+        <v>511338</v>
       </c>
       <c r="R14" t="n">
-        <v>6976405</v>
+        <v>6976453</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1915,11 +1920,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134414148</v>
+        <v>134414651</v>
       </c>
       <c r="B15" t="n">
-        <v>92392</v>
+        <v>92238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511338</v>
+        <v>511450</v>
       </c>
       <c r="R15" t="n">
-        <v>6976453</v>
+        <v>6976390</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134413313</v>
+        <v>134414770</v>
       </c>
       <c r="B16" t="n">
-        <v>58415</v>
+        <v>101298</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102999</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511390</v>
+        <v>511446</v>
       </c>
       <c r="R16" t="n">
-        <v>6976406</v>
+        <v>6976414</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134414770</v>
+        <v>134413313</v>
       </c>
       <c r="B17" t="n">
-        <v>101291</v>
+        <v>58415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>102999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511446</v>
+        <v>511390</v>
       </c>
       <c r="R17" t="n">
-        <v>6976414</v>
+        <v>6976406</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>134414517</v>
       </c>
       <c r="B18" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>134413364</v>
       </c>
       <c r="B19" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134414966</v>
+        <v>134413445</v>
       </c>
       <c r="B20" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511428</v>
+        <v>511377</v>
       </c>
       <c r="R20" t="n">
-        <v>6976444</v>
+        <v>6976424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134413445</v>
+        <v>134414966</v>
       </c>
       <c r="B21" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511377</v>
+        <v>511428</v>
       </c>
       <c r="R21" t="n">
-        <v>6976424</v>
+        <v>6976444</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
         <v>134413333</v>
       </c>
       <c r="B22" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 23809-2026 artfynd.xlsx
+++ b/artfynd/A 23809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134413066</v>
+        <v>134414651</v>
       </c>
       <c r="B2" t="n">
-        <v>101298</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511425</v>
+        <v>511450</v>
       </c>
       <c r="R2" t="n">
-        <v>6976415</v>
+        <v>6976390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134414404</v>
+        <v>134414148</v>
       </c>
       <c r="B3" t="n">
-        <v>101298</v>
+        <v>92406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511387</v>
+        <v>511338</v>
       </c>
       <c r="R3" t="n">
-        <v>6976418</v>
+        <v>6976453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134414533</v>
+        <v>134414632</v>
       </c>
       <c r="B4" t="n">
-        <v>101298</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511451</v>
+        <v>511450</v>
       </c>
       <c r="R4" t="n">
-        <v>6976389</v>
+        <v>6976390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134413390</v>
+        <v>134413239</v>
       </c>
       <c r="B5" t="n">
-        <v>101298</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511381</v>
+        <v>511439</v>
       </c>
       <c r="R5" t="n">
-        <v>6976427</v>
+        <v>6976393</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134413080</v>
+        <v>134413420</v>
       </c>
       <c r="B6" t="n">
-        <v>101298</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511431</v>
+        <v>511380</v>
       </c>
       <c r="R6" t="n">
-        <v>6976419</v>
+        <v>6976427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134414747</v>
+        <v>134414845</v>
       </c>
       <c r="B7" t="n">
-        <v>101298</v>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511458</v>
+        <v>511437</v>
       </c>
       <c r="R7" t="n">
-        <v>6976416</v>
+        <v>6976423</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134415071</v>
+        <v>134413055</v>
       </c>
       <c r="B8" t="n">
-        <v>101298</v>
+        <v>41675</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511415</v>
+        <v>511428</v>
       </c>
       <c r="R8" t="n">
-        <v>6976438</v>
+        <v>6976422</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134414632</v>
+        <v>134413313</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>58415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511450</v>
+        <v>511390</v>
       </c>
       <c r="R9" t="n">
-        <v>6976390</v>
+        <v>6976406</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134414325</v>
+        <v>134413505</v>
       </c>
       <c r="B10" t="n">
-        <v>101298</v>
+        <v>58415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>102999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511385</v>
+        <v>511368</v>
       </c>
       <c r="R10" t="n">
-        <v>6976455</v>
+        <v>6976471</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134413505</v>
+        <v>134413983</v>
       </c>
       <c r="B11" t="n">
-        <v>58415</v>
+        <v>103764</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>222004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511368</v>
+        <v>511363</v>
       </c>
       <c r="R11" t="n">
-        <v>6976471</v>
+        <v>6976469</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1650,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134413055</v>
+        <v>134413333</v>
       </c>
       <c r="B12" t="n">
-        <v>41675</v>
+        <v>101403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100453</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511428</v>
+        <v>511373</v>
       </c>
       <c r="R12" t="n">
-        <v>6976422</v>
+        <v>6976403</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134414708</v>
+        <v>134413066</v>
       </c>
       <c r="B13" t="n">
-        <v>101298</v>
+        <v>101305</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,13 +1777,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511459</v>
+        <v>511425</v>
       </c>
       <c r="R13" t="n">
-        <v>6976405</v>
+        <v>6976415</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1818,11 +1813,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134414148</v>
+        <v>134413080</v>
       </c>
       <c r="B14" t="n">
-        <v>92399</v>
+        <v>101305</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511338</v>
+        <v>511431</v>
       </c>
       <c r="R14" t="n">
-        <v>6976453</v>
+        <v>6976419</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134414651</v>
+        <v>134413364</v>
       </c>
       <c r="B15" t="n">
-        <v>92238</v>
+        <v>101305</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511450</v>
+        <v>511390</v>
       </c>
       <c r="R15" t="n">
-        <v>6976390</v>
+        <v>6976437</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134414770</v>
+        <v>134413390</v>
       </c>
       <c r="B16" t="n">
-        <v>101298</v>
+        <v>101305</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511446</v>
+        <v>511381</v>
       </c>
       <c r="R16" t="n">
-        <v>6976414</v>
+        <v>6976427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134413313</v>
+        <v>134413445</v>
       </c>
       <c r="B17" t="n">
-        <v>58415</v>
+        <v>101305</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102999</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511390</v>
+        <v>511377</v>
       </c>
       <c r="R17" t="n">
-        <v>6976406</v>
+        <v>6976424</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2237,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134414517</v>
+        <v>134414325</v>
       </c>
       <c r="B18" t="n">
-        <v>101298</v>
+        <v>101305</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511459</v>
+        <v>511385</v>
       </c>
       <c r="R18" t="n">
-        <v>6976392</v>
+        <v>6976455</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134413364</v>
+        <v>134414404</v>
       </c>
       <c r="B19" t="n">
-        <v>101298</v>
+        <v>101305</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511390</v>
+        <v>511387</v>
       </c>
       <c r="R19" t="n">
-        <v>6976437</v>
+        <v>6976418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2431,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134413445</v>
+        <v>134414517</v>
       </c>
       <c r="B20" t="n">
-        <v>101298</v>
+        <v>101305</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2466,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511377</v>
+        <v>511459</v>
       </c>
       <c r="R20" t="n">
-        <v>6976424</v>
+        <v>6976392</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2528,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134414966</v>
+        <v>134414533</v>
       </c>
       <c r="B21" t="n">
-        <v>101298</v>
+        <v>101305</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2563,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511428</v>
+        <v>511451</v>
       </c>
       <c r="R21" t="n">
-        <v>6976444</v>
+        <v>6976389</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134413333</v>
+        <v>134414708</v>
       </c>
       <c r="B22" t="n">
-        <v>101396</v>
+        <v>101305</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511373</v>
+        <v>511459</v>
       </c>
       <c r="R22" t="n">
-        <v>6976403</v>
+        <v>6976405</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2696,6 +2686,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2719,6 +2714,884 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134414747</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>511458</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6976416</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134414770</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>511446</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6976414</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134414966</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>511428</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6976444</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134415071</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>511415</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6976438</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134413229</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>511440</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6976392</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134413492</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>511370</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6976445</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134414940</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>511428</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6976446</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134413375</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>511386</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6976433</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134413833</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gällö, Gällö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>511365</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6976471</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23809-2026 artfynd.xlsx
+++ b/artfynd/A 23809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414651</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414632</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413239</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413420</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414845</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413055</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413313</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413505</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413983</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413333</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413066</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413080</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413364</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413390</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413445</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414325</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414404</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414517</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414533</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414708</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414747</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414770</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414966</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134415071</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,6 +3334,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413229</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3301,6 +3436,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413492</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3398,6 +3538,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414940</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3495,6 +3640,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413375</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3592,8 +3742,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134413833</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>